--- a/data/MEN BPS.xlsx
+++ b/data/MEN BPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/Speciale/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/idasofieadrian/Desktop/DTU/SPECIALE/Speciale/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B454AF-F635-8D4A-A0FC-83A998B37EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACC4286-0545-B943-BC02-07BE8B06F3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14480" yWindow="660" windowWidth="14160" windowHeight="15820" xr2:uid="{11AF68D7-8B86-B441-A705-10EDDC882D7C}"/>
   </bookViews>
@@ -499,7 +499,7 @@
         <v>0.71799999999999997</v>
       </c>
       <c r="G2" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -522,7 +522,7 @@
         <v>0.56779999999999997</v>
       </c>
       <c r="G3" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -545,7 +545,7 @@
         <v>3.1821000000000002</v>
       </c>
       <c r="G4" s="2">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
